--- a/imputation_plan/summary report.xlsx
+++ b/imputation_plan/summary report.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Care2Data\rule_injection_validation_framework\imputation_plan\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E511C1C-5687-4C80-8864-4F099377057E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{5EFF87C1-154B-4F8F-BCAC-5501E1FE5B75}"/>
+    <workbookView windowWidth="28800" windowHeight="12180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="skipped_rules" sheetId="1" r:id="rId1"/>
@@ -18,9 +12,6 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -28,6 +19,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,9 +28,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="112">
   <si>
     <t>Batch_name</t>
+  </si>
+  <si>
+    <t>Skipped_RuleID</t>
   </si>
   <si>
     <t>B01_DM_dates</t>
@@ -109,6 +105,10 @@
   </si>
   <si>
     <t>B08_Findings_structural</t>
+  </si>
+  <si>
+    <t>SD1261
+SD1262</t>
   </si>
   <si>
     <t>B09_AllDomain_columns_and_derived_DY</t>
@@ -143,9 +143,6 @@
 SD1380</t>
   </si>
   <si>
-    <t>Skipped_RuleID</t>
-  </si>
-  <si>
     <t>B11_Relationship_RELREC_SUPP</t>
   </si>
   <si>
@@ -196,33 +193,250 @@
     <t>SD1127</t>
   </si>
   <si>
-    <t>SD1261
-SD1262</t>
-  </si>
-  <si>
     <t>Batch_Name</t>
   </si>
   <si>
     <t>RuleId</t>
   </si>
   <si>
-    <t>SD0083
-SD1001
-SD1002
-SD1210
-SD1349</t>
+    <t>SD0083</t>
+  </si>
+  <si>
+    <t>SD1001</t>
+  </si>
+  <si>
+    <t>SD1002</t>
+  </si>
+  <si>
+    <t>SD1210</t>
+  </si>
+  <si>
+    <t>SD1349</t>
+  </si>
+  <si>
+    <t>SD1004</t>
+  </si>
+  <si>
+    <t>SD1034</t>
+  </si>
+  <si>
+    <t>SD1133</t>
+  </si>
+  <si>
+    <t>SD1134</t>
+  </si>
+  <si>
+    <t>SD1322</t>
+  </si>
+  <si>
+    <t>SD1360</t>
+  </si>
+  <si>
+    <t>SD2003</t>
+  </si>
+  <si>
+    <t>SD2022</t>
+  </si>
+  <si>
+    <t>SD2023</t>
+  </si>
+  <si>
+    <t>B03_SpecialPurpose_SE_SM_SV_DI</t>
+  </si>
+  <si>
+    <t>SD1027</t>
+  </si>
+  <si>
+    <t>SD1050</t>
+  </si>
+  <si>
+    <t>SD1099</t>
+  </si>
+  <si>
+    <t>SD1352</t>
+  </si>
+  <si>
+    <t>B05_Events_AE_DS_MH_DV</t>
+  </si>
+  <si>
+    <t>SD1075</t>
+  </si>
+  <si>
+    <t>SD1143</t>
+  </si>
+  <si>
+    <t>SD1201</t>
+  </si>
+  <si>
+    <t>SD1242</t>
+  </si>
+  <si>
+    <t>SD1313</t>
+  </si>
+  <si>
+    <t>SD1440</t>
+  </si>
+  <si>
+    <t>SD0007</t>
+  </si>
+  <si>
+    <t>SD0040</t>
+  </si>
+  <si>
+    <t>SD1043</t>
+  </si>
+  <si>
+    <t>SD1272</t>
+  </si>
+  <si>
+    <t>SD1117</t>
+  </si>
+  <si>
+    <t>SD1439</t>
+  </si>
+  <si>
+    <t>SD1445</t>
+  </si>
+  <si>
+    <t>SD0058</t>
+  </si>
+  <si>
+    <t>SD1074</t>
+  </si>
+  <si>
+    <t>SD1076</t>
+  </si>
+  <si>
+    <t>SD1079</t>
+  </si>
+  <si>
+    <t>SD1083</t>
+  </si>
+  <si>
+    <t>SD1244</t>
+  </si>
+  <si>
+    <t>SD1245</t>
+  </si>
+  <si>
+    <t>SD1246</t>
+  </si>
+  <si>
+    <t>SD0004</t>
+  </si>
+  <si>
+    <t>SD0005</t>
+  </si>
+  <si>
+    <t>SD0036</t>
+  </si>
+  <si>
+    <t>SD0051</t>
+  </si>
+  <si>
+    <t>SD0052</t>
+  </si>
+  <si>
+    <t>SD1011</t>
+  </si>
+  <si>
+    <t>SD1015</t>
+  </si>
+  <si>
+    <t>SD1300</t>
+  </si>
+  <si>
+    <t>SD0046</t>
+  </si>
+  <si>
+    <t>SD0086</t>
+  </si>
+  <si>
+    <t>SD1126</t>
+  </si>
+  <si>
+    <t>SD1130</t>
+  </si>
+  <si>
+    <t>B12_TrialDesign_TA_TE_TI_TV_TD</t>
+  </si>
+  <si>
+    <t>SD1052</t>
+  </si>
+  <si>
+    <t>SD1064</t>
+  </si>
+  <si>
+    <t>SD1068</t>
+  </si>
+  <si>
+    <t>SD1267</t>
+  </si>
+  <si>
+    <t>SD1286</t>
+  </si>
+  <si>
+    <t>SD1378</t>
+  </si>
+  <si>
+    <t>B13_TrialSummary_TS_part1</t>
+  </si>
+  <si>
+    <t>SD1038</t>
+  </si>
+  <si>
+    <t>SD1268</t>
+  </si>
+  <si>
+    <t>SD1278</t>
+  </si>
+  <si>
+    <t>SD1297</t>
+  </si>
+  <si>
+    <t>SD2018</t>
+  </si>
+  <si>
+    <t>SD2266</t>
+  </si>
+  <si>
+    <t>SD1220</t>
+  </si>
+  <si>
+    <t>SD1307</t>
+  </si>
+  <si>
+    <t>SD2017</t>
+  </si>
+  <si>
+    <t>B25_Mixed</t>
+  </si>
+  <si>
+    <t>SD1221</t>
+  </si>
+  <si>
+    <t>SD1225</t>
+  </si>
+  <si>
+    <t>SD1299</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -231,16 +445,353 @@
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -248,31 +799,320 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -321,7 +1161,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -354,26 +1194,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -406,23 +1229,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -564,22 +1370,17 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFACAC94-9A65-44D6-9A9D-4035F54AE4C8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="39.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.2857142857143" customWidth="1"/>
+    <col min="2" max="2" width="15.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -587,175 +1388,614 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" ht="45" spans="1:2">
       <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="60">
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" ht="60" spans="1:2">
       <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="45">
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" ht="45" spans="1:2">
       <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="240">
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" ht="240" spans="1:2">
       <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="90">
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" ht="90" spans="1:2">
       <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="90">
+      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" ht="90" spans="1:2">
       <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="30">
+      <c r="B7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" ht="30" spans="1:2">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="315">
+        <v>16</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" ht="315" spans="1:2">
       <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="45">
-      <c r="A11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="1" t="s">
+    </row>
+    <row r="11" ht="45" spans="1:2">
+      <c r="A11" s="4" t="s">
         <v>20</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="1" t="s">
         <v>22</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="1" t="s">
         <v>24</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="2" t="s">
         <v>26</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="1" t="s">
         <v>28</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="B16" s="2" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="2" t="s">
+      <c r="A17" s="4" t="s">
         <v>32</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="1" t="s">
         <v>34</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F16DE7D8-B6D7-4020-9343-940E714F9FB6}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B70"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="45" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="75">
-      <c r="A2" t="s">
-        <v>1</v>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>38</v>
       </c>
     </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="1"/>
+      <c r="B58" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="1"/>
+      <c r="B61" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="1"/>
+      <c r="B62" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="1"/>
+      <c r="B63" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="1"/>
+      <c r="B66" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="1"/>
+      <c r="B67" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="1"/>
+      <c r="B69" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="1"/>
+      <c r="B70" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>